--- a/data_extactor/batch_10_fa/batch_0030_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0030_fa.xlsx
@@ -493,12 +493,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawyers (وکلا)</t>
+          <t>وکلا (Lawyers)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Attorney | Attorney General | Attorney at Law | Counsel | County Attorney | District Attorney | General Counsel | Lawyer | Prosecuting Attorney | Prosecutor</t>
+          <t>وکیل | دادستان کل | وکیل دادگستری | مشاور حقوقی | وکیل شهرستان | دادستان ناحیه | مشاور حقوقی ارشد | وکیل | وکیل دادستانی | دادستان</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنرانی | گوش دادن فعال | درک مطلب | تفکر انتقادی | نوشتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | درک شفاهی | بیان نوشتاری | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | سازماندهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری دسته‌بندی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | فشار زمانی | نتایج کاری و خروجی‌های سایر کارکنان | محیط داخلی و کنترل‌شده از نظر محیطی | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | ارزیابان، بازرسان و محققان خسارت | افسران انطباق | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | اساتید حقوق، پس از متوسطه | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و محققان خصوصی | بازرسان و مأموران مالیاتی و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | مدرسان حقوق، آموزش عالی | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و بازرسان خصوصی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Judicial Law Clerks (کارمندان حقوقی قضایی)</t>
+          <t>کارمندان حقوقی قضایی (Judicial Law Clerks)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Appellate Law Clerk | Career Judicial Law Clerk | Career Law Clerk | Judicial Assistant | Judicial Clerk | Judicial Law Clerk | Law Clerk | Law Researcher | Pro Se Law Clerk | Term Law Clerk</t>
+          <t>کارآموز حقوقی دادگاه تجدیدنظر | کارآموز حقوقی دائمی دستگاه قضایی | کارآموز حقوقی دائمی | دستیار قضایی | منشی قضایی | کارآموز حقوقی قضایی | کارآموز حقوقی | پژوهشگر حقوق | کارآموز حقوقی پرونده‌های بدون وکیل | کارآموز حقوقی دوره‌ای</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نوشتن | صحبت کردن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | درک شفاهی | بیان شفاهی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | ایمیل | اهمیت دقیق یا صحیح بودن | بحث‌های رودررو با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | فشار زمانی | تناوب تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | فشار زمانی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مأموران انتظامی دادگاه | ارزیابان، بازرسان و محققان خسارت | افسران انطباق | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | اساتید حقوق، پس از متوسطه | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | افسران گشت پلیس و کلانتر | کارآگاهان و محققان خصوصی | افسران آزادی مشروط و متخصصان درمان اصلاحی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | ضابطان دادگستری | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | مدرسان حقوق، آموزش عالی | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Administrative Law Judges, Adjudicators, and Hearing Officers (قضات حقوق اداری، داوران و مسئولان رسیدگی)</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی (Administrative Law Judges, Adjudicators, and Hearing Officers)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adjudications Specialist | Adjudicator | Administrative Hearings Officer | Administrative Judge | Administrative Law Judge | Appeals Examiner | Appeals Referee | Claims Adjudicator | Hearings Officer | Workers' Compensation Hearings Officer</t>
+          <t>کارشناس رسیدگی و صدور رأی | رسیدگی‌کننده و صادرکننده رأی | مسئول جلسات استماع اداری | قاضی اداری | قاضی حقوق اداری | کارشناس رسیدگی به تجدیدنظر | داور تجدیدنظر | ارزیاب خسارت | مسئول جلسات استماع | مسئول جلسات استماع غرامت کارگران</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | صحبت کردن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | پزشکی و دندانپزشکی | مدیریت و اداره</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | پزشکی و دندان‌پزشکی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک نوشتاری | درک شفاهی | بیان نوشتاری | استدلال قیاسی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | سازماندهی اطلاعات | دید نزدیک | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>استدلال استقرایی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | صرف زمان برای نشستن | ایمیل | تناوب تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت تکرار وظایف مشابه | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ایمیل | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | ارزیابان، بازرسان و محققان خسارت | افسران انطباق | بازرسان جنازه | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | افسران گشت پلیس و کلانتر | افسران آزادی مشروط و متخصصان درمان اصلاحی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
+          <t>داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | بازرسان مرگ | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان، محققان و تحلیلگران کلاهبرداری | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | ماموران گشت پلیس و کلانتر | افسران مشروط و متخصصان درمان اصلاحی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arbitrators, Mediators, and Conciliators (داوران، میانجی‌گران و مصالحه‌گران)</t>
+          <t>داوران، میانجی‌گران و مصالحه‌گران (Arbitrators, Mediators, and Conciliators)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alternative Dispute Resolution Coordinator (ADR Coordinator) | Arbiter | Arbitrator | Divorce Mediator | Family Mediator | Federal Mediator | Labor Arbitrator | Labor Mediator | Mediator | Public Employment Mediator</t>
+          <t>هماهنگ‌کننده حل اختلاف جایگزین (ADR) | داور | داور حل اختلاف | میانجی طلاق | میانجی خانواده | میانجی فدرال | داور اختلافات کارگری | میانجی اختلافات کارگری | میانجی | میانجی اشتغال بخش عمومی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نوشتن | صحبت کردن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک نوشتاری | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | توجه انتخابی | سازماندهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | خلاقیت</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران</t>
+          <t>صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | ارزیابان، بازرسان و محققان خسارت | مدیران انطباق | افسران انطباق | کارمندان دادگاه، شهرداری و مجوزها | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | بازرسان، محققان و تحلیلگران کلاهبرداری | بازرسان و محققان اموال دولتی | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیلگران مدیریت | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و محققان خصوصی</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | مدیران انطباق | افسران انطباق | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | بازرسان، محققان و تحلیلگران کلاهبرداری | بازرسان و محققان اموال دولتی | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | متخصصان روابط کار | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و بازرسان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Judges, Magistrate Judges, and Magistrates (قضات، قضات دادگاه‌های بدوی و قضات صلح)</t>
+          <t>قضات، قضات دادگاه‌های بدوی و قضات صلح (Judges, Magistrate Judges, and Magistrates)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Circuit Court Judge | Circuit Judge | County Judge | Court of Appeals Judge | District Court Judge | Judge | Justice of the Peace | Magisterial District Judge | Magistrate | Superior Court Judge</t>
+          <t>قاضی دادگاه بخش | قاضی حوزه قضایی | قاضی شهرستان | قاضی دادگاه تجدیدنظر | قاضی دادگاه ناحیه | قاضی | قاضی صلح | قاضی ناحیه قضایی | قاضی دادگاه بدوی | قاضی دادگاه عالی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نوشتن | صحبت کردن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | روانشناسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال قیاسی | درک نوشتاری | استدلال استقرایی | بیان شفاهی | بیان نوشتاری | وضوح گفتار | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | خلاقیت | روانی ایده‌ها</t>
+          <t>درک شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | بیان کتبی | وضوح گفتار | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>محیط داخلی و کنترل‌شده از نظر محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | ارتباط با دیگران | تناوب تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | مکالمات تلفنی | سخنرانی عمومی | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | ارتباط با دیگران | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | مکالمات تلفنی | سخنرانی عمومی | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مأموران انتظامی دادگاه | افسران انطباق | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | اساتید عدالت کیفری و اجرای قانون، پس از متوسطه | کارآگاهان و بازرسان جنایی | نمایندگان و افسران فرصت‌های برابر | سرپرستان رده‌اول افسران اصلاحی | سرپرستان رده‌اول پلیس و کارآگاهان | کارمندان حقوقی قضایی | متخصصان روابط کار | اساتید حقوق، پس از متوسطه | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | افسران گشت پلیس و کلانتر | کارآگاهان و محققان خصوصی | افسران آزادی مشروط و متخصصان درمان اصلاحی</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | ضابطان دادگستری | افسران انطباق | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | کارآگاهان و بازرسان جنایی | نمایندگان و افسران فرصت‌های برابر | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | کارمندان حقوقی قضایی | متخصصان روابط کار | مدرسان حقوق، آموزش عالی | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,22 +778,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paralegals and Legal Assistants (پارالیگال‌ها و دستیاران حقوقی)</t>
+          <t>پارالیگال‌ها و دستیاران حقوقی (Paralegals and Legal Assistants)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Immigration Paralegal | Law Associate | Legal Analyst | Legal Assistant | Legal Clerk | Legal Processing Assistant | Litigation Paralegal | Paralegal | Paralegal Specialist | Real Estate Paralegal</t>
+          <t>دستیار حقوقی امور مهاجرت | وکیل همکار | تحلیل‌گر حقوقی | دستیار حقوقی | متصدی امور حقوقی | دستیار پردازش اسناد حقوقی | دستیار حقوقی دعاوی | دستیار حقوقی | کارشناس دستیاری حقوقی | دستیار حقوقی املاک</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AbacusNext HotDocs | Adobe Acrobat | American LegalNet USCourtForms | Appligent Citation FDFMerge | Blumbeg Drafting Libraries | Bowne JFS Litigator's Notebook | Bridgeway eCounsel | نرم‌افزار تحلیل پرونده | CaseSoft DepPrep | CaseSoft TextMap | CaseSoft TimeMap | نرم‌افزار کاتالوگ دسترسی رایانه‌ای | Corel WordPerfect Office Suite | Corporate Focus Solium Shareworks | نرم‌افزار پایگاه داده | Dataflight Opticon | نرم‌افزار قرارداد دیجیتال | نرم‌افزار سیستم مدیریت اسناد | Dropbox | نرم‌افزار کشف الکترونیکی | نرم‌افزار مدیریت رونویسی دیجیتال | Fastcase legal software | FindForms | FindLaw Code of Federal Regulations CFR | Fund Software ATIDS | Google Docs | Google Drive | نرم‌افزار Google Workspace | IBM Notes | Inmagic DB/TextWorks | IntelliPDF CURVES | Intuit QuickBooks | Iron Mountain Accutrac records management software | LawManager | نرم‌افزار اسناد حقوقی | LexisNexis | LexisNexis Applied Discovery | LexisNexis CaseMap | LexisNexis CheckCite | LexisNexis CodeMaster | LexisNexis Company Analyzer | LexisNexis Concordance | LexisNexis CourtLink Strategic Profiles | LexisNexis File and Serve | LexisNexis SmartLinx | LexisNexis Time Matters | LexisNexis Total Search | نرم‌افزار پشتیبانی دادرسی | MicroStrategy | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Word | NetDocuments | Nuance Power PDF | OmniRIM Records Management Suite | نرم‌افزار جستجو و بازیابی پایگاه داده آنلاین | نرم‌افزار جستجوی سوابق عمومی آنلاین | نرم‌افزار جستجوی سند و گزارش املاک آنلاین | نرم‌افزار تشخیص نوری کاراکتر OCR | Orion Law Management Systems Orion | Ovid SilverPlatter WebSPIRS | PDF Snake Easy Bates | نرم‌افزار مدیریت تمرین PMS | ProForce Paralegal Pro-Pack | نرم‌افزار مدیریت سوابق | نرم‌افزار پایگاه داده رابطه‌ای | Relativity e-Discovery | Saga Practice Manager | Software Technology PracticeMaster | Summation Blaze | Sure Will Writer | THOMAS Global Register | نرم‌افزار مالیاتی | The Sackett Group MacPac for Legal | Thomson CompuMark SAEGIS | Thomson Reuters LiveNote Stream | Thomson Reuters Westlaw | Thomson Reuters Westlaw Edge | Thomson West FindLaw | Thomson West ProLaw | TrialWorks | Tumbleweed SecureTransport | Uniscribe | نرم‌افزار مرورگر وب | Wilson's Computer Applications RealEasy Appraisals | Zoom | Zylab ZyImage | a la mode WinTOTAL | dtSearch | نرم‌افزار مدیریت اسناد iManage</t>
+          <t>AbacusNext HotDocs | Adobe Acrobat | American LegalNet USCourtForms | Appligent Citation FDFMerge | Blumbeg Drafting Libraries | Bowne JFS Litigator's Notebook | Bridgeway eCounsel | نرم‌افزار تحلیل پرونده | CaseSoft DepPrep | CaseSoft TextMap | CaseSoft TimeMap | نرم‌افزار کاتالوگ دسترسی رایانه‌ای | Corel WordPerfect Office Suite | Corporate Focus Solium Shareworks | نرم‌افزار پایگاه داده | Dataflight Opticon | نرم‌افزار قرارداد دیجیتال | نرم‌افزار سیستم مدیریت اسناد | Dropbox | نرم‌افزار کشف الکترونیکی | نرم‌افزار مدیریت رونویسی دیجیتال | Fastcase legal software | FindForms | FindLaw Code of Federal Regulations CFR | Fund Software ATIDS | Google Docs | Google Drive | نرم‌افزار Google Workspace | IBM Notes | Inmagic DB/TextWorks | IntelliPDF CURVES | Intuit QuickBooks | Iron Mountain Accutrac records management software | LawManager | نرم‌افزار اسناد حقوقی | LexisNexis | LexisNexis Applied Discovery | LexisNexis CaseMap | LexisNexis CheckCite | LexisNexis CodeMaster | LexisNexis Company Analyzer | LexisNexis Concordance | LexisNexis CourtLink Strategic Profiles | LexisNexis File and Serve | LexisNexis SmartLinx | LexisNexis Time Matters | LexisNexis Total Search | نرم‌افزار پشتیبانی دادرسی | MicroStrategy | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Word | NetDocuments | Nuance Power PDF | OmniRIM Records Management Suite | نرم‌افزار جستجو و بازیابی پایگاه داده آنلاین | نرم‌افزار جستجوی سوابق عمومی آنلاین | نرم‌افزار جستجوی عنوان آنلاین و گزارش ملک | نرم‌افزار تشخیص نوری کاراکتر OCR | Orion Law Management Systems Orion | Ovid SilverPlatter WebSPIRS | PDF Snake Easy Bates | نرم‌افزار مدیریت مطب PMS | ProForce Paralegal Pro-Pack | نرم‌افزار مدیریت سوابق | نرم‌افزار پایگاه داده رابطه‌ای | Relativity e-Discovery | Saga Practice Manager | Software Technology PracticeMaster | Summation Blaze | Sure Will Writer | THOMAS Global Register | نرم‌افزار مالیاتی | The Sackett Group MacPac for Legal | Thomson CompuMark SAEGIS | Thomson Reuters LiveNote Stream | Thomson Reuters Westlaw | Thomson Reuters Westlaw Edge | Thomson West FindLaw | Thomson West ProLaw | TrialWorks | Tumbleweed SecureTransport | Uniscribe | نرم‌افزار مرورگر وب | Wilson's Computer Applications RealEasy Appraisals | Zoom | Zylab ZyImage | a la mode WinTOTAL | dtSearch | نرم‌افزار مدیریت اسناد iManage</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نوشتن | درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک شفاهی | بیان شفاهی | بیان نوشتاری | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی و کنترل‌شده از نظر محیطی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | ارزیابان، بازرسان و محققان خسارت | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | متخصصان سوابق پزشکی | کارمندان اداری، عمومی | کارآگاهان و محققان خصوصی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
+          <t>حسابداران و حسابرسان | قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | متخصصان مدارک پزشکی | کارمندان دفتری عمومی | کارآگاهان و بازرسان خصوصی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Title Examiners, Abstractors, and Searchers (بازرسان اسناد، خلاصه‌نویسان و جستجوگران)</t>
+          <t>بازرسان اسناد، خلاصه‌نویسان و جستجوگران (Title Examiners, Abstractors, and Searchers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abstractor | Commercial Title Examiner | Searcher | Title Abstractor | Title Agent | Title Examiner | Title Officer | Title Searcher</t>
+          <t>خلاصه‌نویس اسناد | کارشناس بررسی اسناد مالکیت تجاری | جست‌وجوگر اسناد | خلاصه‌نویس اسناد مالکیت | نماینده اسناد مالکیت | کارشناس بررسی اسناد مالکیت | مسئول اسناد مالکیت | جست‌وجوگر اسناد مالکیت</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | نوشتن | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | تشخیص گفتار | دید نزدیک | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستار | سازماندهی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | ایمیل | محیط داخلی و کنترل‌شده از نظر محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | تناوب تصمیم‌گیری | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری</t>
+          <t>اهمیت دقیق یا درست بودن | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان املاک | ارزیابان اموال شخصی و تجاری | کارمندان دفترداری، حسابداری و حسابرسی | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و نویسندگان همزمان | کارمندان دادگاه، شهرداری و مجوزها | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | متخصصان مدیریت اسناد | کارمندان بایگانی | بازرسان و محققان اموال دولتی | کارمندان پردازش ادعاها و سیاست‌های بیمه | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان وام و کارمندان | متخصصان سوابق پزشکی | پارالیگال‌ها و دستیاران حقوقی | دستیاران آماری | بازرسان و مأموران مالیاتی و مأموران درآمد</t>
+          <t>ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | کارمندان دفترداری، حسابداری و حسابرسی | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | متخصصان مدیریت اسناد | کارمندان بایگانی | بازرسان و محققان اموال دولتی | کارمندان پردازش بیمه و بیمه‌نامه | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان و کارمندان وام | متخصصان مدارک پزشکی | پارالیگال‌ها و دستیاران حقوقی | دستیاران آماری | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Legal Support Workers, All Other (کارکنان پشتیبانی حقوقی، سایر)</t>
+          <t>کارکنان پشتیبانی حقوقی، سایر (Legal Support Workers, All Other)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compliance Assistant | Contract Administrator | Court Clerk | Docket Clerk | Legal Analyst | Legal Assistant | Legal Research Assistant | Litigation Support Specialist | Patent Agent | Legal Support Specialist</t>
+          <t>دستیار انطباق | مسئول امور قراردادها | منشی دادگاه | متصدی دفتر ثبت پرونده | تحلیل‌گر حقوقی | دستیار حقوقی | دستیار پژوهش حقوقی | کارشناس پشتیبانی دعاوی | نماینده ثبت اختراع | کارشناس پشتیبانی حقوقی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی و کنترل‌شده از نظر محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پارالیگال‌ها و دستیاران حقوقی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | کارمندان حقوقی قضایی | وکلا | داوران، میانجی‌گران و مصالحه‌گران | قضات حقوق اداری، داوران و مسئولان رسیدگی | قضات، قضات دادگاه‌های بدوی و قضات صلح | گزارشگران دادگاه و نویسندگان همزمان | افسران انطباق | متخصصان امور نظارتی | ارزیابان، بازرسان و محققان خسارت | متخصصان منابع انسانی | منشی‌های حقوقی و دستیاران اداری | منشی‌های اجرایی و دستیاران اداری اجرایی | متخصصان مدیریت اسناد | تحلیلگران مدیریت | اساتید حقوق، پس از متوسطه | بازرسان، محققان و تحلیلگران کلاهبرداری | بیمه‌گران | بازرسان مالی</t>
+          <t>پارالیگال‌ها و دستیاران حقوقی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | کارمندان حقوقی قضایی | وکلا | داوران، میانجی‌گران و مصالحه‌گران | قضات حقوق اداری، داوران و مسئولان رسیدگی | قضات، قضات دادگاه‌های بدوی و قضات صلح | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | افسران انطباق | متخصصان امور نظارتی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | متخصصان منابع انسانی | منشی‌های حقوقی و دستیاران اداری | منشی‌های اجرایی و دستیاران اداری اجرایی | متخصصان مدیریت اسناد | تحلیل‌گران مدیریت | مدرسان حقوق، آموزش عالی | بازرسان، محققان و تحلیلگران کلاهبرداری | بیمه‌گران | بازرسان مالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Business Teachers, Postsecondary (اساتید کسب‌وکار، پس از متوسطه)</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه (Business Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accounting Instructor | Accounting Professor | Associate Professor | Business Administration Professor | Business Instructor | Business Professor | Instructor | Management Professor | Marketing Professor | Professor</t>
+          <t>مدرس حسابداری | استاد حسابداری | دانشیار | استاد مدیریت بازرگانی | مدرس بازرگانی | استاد بازرگانی | مدرس | استاد مدیریت | استاد بازاریابی | استاد</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Almaris E-Learning Systems Financial Accounting Tutor | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار LMS Desire2Learn | نرم‌افزار ایمیل | Google Docs | Google Gmail | Google Scholar | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | Instructure Canvas | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | R | SAS | Sage 50 Accounting | Sakai CLE | Schoology | StataCorp Stata | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Almaris E-Learning Systems Financial Accounting Tutor | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | Google Gmail | Google Scholar | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | Instructure Canvas | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | R | SAS | Sage 50 Accounting | Sakai CLE | Schoology | StataCorp Stata | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>صحبت کردن | راهبردهای یادگیری | نوشتن | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | قانون و دولت | رایانه و الکترونیک | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | روانشناسی | اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | قانون و دولت | رایانه و الکترونیک | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | بیان نوشتاری | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تسهیل اعداد | خلاقیت | روانی ایده‌ها | توجه انتخابی</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | اصالت | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی و کنترل‌شده از نظر محیطی | سخنرانی عمومی | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | فشار زمانی | تناوب تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | فشار زمانی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | معلمان آموزش شغلی/فنی، دوره متوسطه | معلمان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره دبیرستان | معلمان ارتباطات، پس از متوسطه | معلمان علوم رایانه، پس از متوسطه | معلمان اقتصاد، پس از متوسطه | مدیران آموزش، پس از متوسطه | معلمان آموزش و پرورش، پس از متوسطه | معلمان علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | اساتید حقوق، پس از متوسطه | معلمان علوم کتابداری، پس از متوسطه | تحلیلگران مدیریت | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | معلمان علوم سیاسی، پس از متوسطه | معلمان مددکاری اجتماعی، پس از متوسطه | دستیاران آموزشی، پس از متوسطه | متخصصان آموزش و توسعه</t>
+          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان ارتباطات، آموزش عالی | اساتید علوم رایانه، پس از متوسطه | استادان اقتصاد، پس از متوسطه | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان حقوق، آموزش عالی | مدرسان علوم کتابداری، آموزش عالی | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | استادان علوم سیاسی، پس از متوسطه | مدرسان مددکاری اجتماعی، آموزش عالی | دستیاران آموزشی، مقطع پس از متوسطه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,22 +1006,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Computer Science Teachers, Postsecondary (اساتید علوم رایانه، پس از متوسطه)</t>
+          <t>اساتید علوم رایانه، پس از متوسطه (Computer Science Teachers, Postsecondary)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assistant Professor | Associate Professor | Computer Information Systems Instructor (CIS Instructor) | Computer Science Instructor | Computer Science Professor | Faculty Member | Information Technology Instructor (IT Instructor) | Instructor | Lecturer | Professor</t>
+          <t>استادیار | دانشیار | مدرس سامانه‌های اطلاعات رایانه‌ای (CIS) | مدرس علوم رایانه | استاد علوم رایانه | عضو هیئت علمی | مدرس فناوری اطلاعات (IT) | مدرس | مدرس | استاد</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Dreamweaver | Adobe Photoshop | Adobe Premiere Pro | Blackboard Learn | نرم‌افزار Blackboard | C | C# | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار پایگاه داده | نرم‌افزار LMS Desire2Learn | نرم‌افزار ایمیل | نرم‌افزار فایروال | Google Docs | زبان نشانه‌گذاری ابرمتن HTML | سیستم مدیریت یادگیری LMS | Linux | سیستم‌های اطلاعات مدیریت MIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | Moodle | نرم‌افزار تشخیص نفوذ شبکه | نرم‌افزار برنامه‌نویسی شیءگرا | OpenAI ChatGPT | Oracle Java | PHP | زبان‌های برنامه‌نویسی | Python | Sakai CLE | ابزارهای توسعه نرم‌افزار | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Dreamweaver | Adobe Photoshop | Adobe Premiere Pro | Blackboard Learn | نرم‌افزار Blackboard | C | C# | C++ | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار پایگاه داده | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | نرم‌افزار فایروال | Google Docs | زبان نشانه‌گذاری ابرمتن HTML | سیستم مدیریت یادگیری LMS | Linux | سیستم‌های اطلاعات مدیریت MIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | Moodle | نرم‌افزار تشخیص نفوذ شبکه | نرم‌افزار برنامه‌نویسی شیءگرا | OpenAI ChatGPT | Oracle Java | PHP | زبان‌های برنامه‌نویسی | Python | Sakai CLE | ابزارهای توسعه نرم‌افزار | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | سازماندهی اطلاعات | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | تسهیل اعداد | استدلال ریاضی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی و کنترل‌شده از نظر محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | سخنرانی عمومی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره متوسطه | معلمان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره دبیرستان | معلمان ارتباطات، پس از متوسطه | مهندسان سخت‌افزار رایانه | برنامه‌نویسان رایانه | تحلیلگران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | دانشمندان تحقیقات رایانه و اطلاعات | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | اساتید مهندسی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | معلمان علوم کتابداری، پس از متوسطه | تحلیلگران مدیریت | معلمان علوم ریاضی، پس از متوسطه | معلمان فیزیک، پس از متوسطه | توسعه‌دهندگان نرم‌افزار | دستیاران آموزشی، پس از متوسطه | معلمان خصوصی</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان ارتباطات، آموزش عالی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان تحقیقات کامپیوتر و اطلاعات | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدرسان مهندسی، پس از متوسطه | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | تحلیل‌گران مدیریت | مدرسان علوم ریاضی، پس از متوسطه | مدرسان فیزیک، پس از متوسطه | توسعه‌دهندگان نرم‌افزار | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0030_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0030_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری نتیجه‌گیری</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | مدیران ارشد اجرایی | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان انطباق و نظارت قانونی | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارآگاهان و کارشناسان بررسی جرایم | کارشناسان مصاحبه احراز شرایط در برنامه‌های دولتی | کارشناسان و بازرسان برابری فرصت‌ها | بازرسان، کارشناسان و تحلیل‌گران بررسی تقلب و تخلفات | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | متخصصان روابط کار | استادان حقوق، آموزش عالی | دبیران و مسئولان دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | کارآگاهان و بازرسان خصوصی | ممیزان مالیاتی، ماموران وصول و ماموران مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | مدیران عامل و مدیران ارشد اجرایی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارآگاهان و بازرسان جنایی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | کارشناسان بازرسی، کشف و تحلیل تقلب | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | کارشناسان روابط کار و امور تشکل‌های کارگری | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | کارآگاهان و بازرسان خصوصی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | ضابطان قضایی و مأموران اجرای احکام دادگاه | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان انطباق و نظارت قانونی | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارآگاهان و کارشناسان بررسی جرایم | کارشناسان مصاحبه احراز شرایط در برنامه‌های دولتی | کارشناسان و بازرسان برابری فرصت‌ها | بازرسان، کارشناسان و تحلیل‌گران بررسی تقلب و تخلفات | قضات دادگاه و دادیاران | استادان حقوق، آموزش عالی | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | مأموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مأموران مراقبت و متخصصان بازپروری و اصلاح و تربیت | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | مأموران انتظامات و حفاظت دادگاه | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارآگاهان و بازرسان جنایی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | کارشناسان بازرسی، کشف و تحلیل تقلب | قضات دادگاه و دادیاران | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری | پزشکی و دندانپزشکی | مدیریت و امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | پزشکی و دندان‌پزشکی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>استدلال استقرایی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>داوران، میانجی‌گران و صلح‌یاران | مدیران ارشد اجرایی | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان انطباق و نظارت قانونی | کارشناسان پزشکی قانونی | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارآگاهان و کارشناسان بررسی جرایم | کارشناسان مصاحبه احراز شرایط در برنامه‌های دولتی | کارشناسان و بازرسان برابری فرصت‌ها | بازرسان، کارشناسان و تحلیل‌گران بررسی تقلب و تخلفات | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | متخصصان روابط کار | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | مأموران گشت پلیس و کلانتری | مأموران مراقبت و متخصصان بازپروری و اصلاح و تربیت | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>داوران، میانجی‌گران و صلح‌یاران | مدیران عامل و مدیران ارشد اجرایی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارآگاهان و بازرسان جنایی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | کارشناسان بازرسی، کشف و تحلیل تقلب | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | کارشناسان روابط کار و امور تشکل‌های کارگری | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | ماموران گشت پلیس و کلانتری | مددکاران قضایی و متخصصان اصلاح و تربیت | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | امور کارکنان و منابع انسانی | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | قانون و دولت | پرسنل و منابع انسانی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | توجه انتخابی | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | ارزیابان، کارشناسان و بازرسان خسارت بیمه | مدیران انطباق و نظارت قانونی | کارشناسان انطباق و نظارت قانونی | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارشناسان مصاحبه احراز شرایط در برنامه‌های دولتی | کارشناسان و بازرسان برابری فرصت‌ها | کارشناسان ارزیابی و بازرسی مالی | بازرسان، کارشناسان و تحلیل‌گران بررسی تقلب و تخلفات | بازرسان و کارشناسان اموال دولتی | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | متخصصان روابط کار | وکلا | دبیران و مسئولان دفاتر حقوقی | تحلیل‌گران و مشاوران مدیریت | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | کارآگاهان و بازرسان خصوصی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | بازرسان و ارزیابان مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | بازرسان و ممیزان اموال دولتی | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | کارشناسان روابط کار و امور تشکل‌های کارگری | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و دستیاران امور حقوقی | کارآگاهان و بازرسان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | مدیریت و امور اداری | روان‌شناسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | بیان کتبی | وضوح گفتار | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | بیان کتبی | وضوح گفتار | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | ضابطان قضایی و مأموران اجرای احکام دادگاه | کارشناسان انطباق و نظارت قانونی | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | مدرسان علوم قضایی، حقوقی و انتظامی، آموزش عالی | کارآگاهان و کارشناسان بررسی جرایم | کارشناسان و بازرسان برابری فرصت‌ها | سرپرستان رده اول زندانبانان و مأموران بازداشتگاه | سرپرستان رده اول افسران پلیس و کارآگاهان | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | متخصصان روابط کار | استادان حقوق، آموزش عالی | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | مأموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مأموران مراقبت و متخصصان بازپروری و اصلاح و تربیت</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | مأموران انتظامات و حفاظت دادگاه | کارشناسان پایش انطباق و بازرسی مقرراتی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | کارآگاهان و بازرسان جنایی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول پلیس و کارآگاهان | کارشناسان پژوهش و تحریر قضایی | کارشناسان روابط کار و امور تشکل‌های کارگری | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان انطباق و نظارت قانونی | کارمندان امور نامه‌نگاری و مکاتبات اداری | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارشناسان مصاحبه احراز شرایط در برنامه‌های دولتی | مسئولان دفاتر و مدیران اجرایی | متصدیان بایگانی و ثبت اسناد | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان سوابق و پرونده‌های پزشکی | کارمندان عمومی امور دفتری | کارآگاهان و بازرسان خصوصی | دبیران و مسئولان دفاتر، به‌جز حقوقی، پزشکی و اجرایی | دستیاران پژوهش علوم اجتماعی | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>حسابداران و حسابرسان | قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان امور دفتری و امور عمومی اداری | کارآگاهان و بازرسان خصوصی | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | قانون و دولت | اداری | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | دید نزدیک | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری نتیجه‌گیری | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ارزیابان و قیمت‌گذاران املاک و مستغلات | ارزیابان اموال منقول و دارایی‌های تجاری | کارمندان امور دفترداری، حسابداری و حسابرسی | کارشناسان انطباق و نظارت قانونی | کارمندان امور نامه‌نگاری و مکاتبات اداری | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارشناسان و کارمندان بررسی و تایید اعتبار | کارشناسان مدیریت اسناد | متصدیان بایگانی و ثبت اسناد | بازرسان و کارشناسان اموال دولتی | کارمندان رسیدگی به خسارت و صدور بیمه‌نامه | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | دبیران و مسئولان دفاتر حقوقی | کارمندان و متصدیان مصاحبه و ثبت وام | کارشناسان سوابق و پرونده‌های پزشکی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | دستیاران آمار | ممیزان مالیاتی، ماموران وصول و ماموران مالیاتی</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | بازرسان و ممیزان اموال دولتی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان و دستیاران امور حقوقی | دستیاران و تکنسین‌های آمار | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | توانایی حفظ و یادآوری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | داوران، میانجی‌گران و صلح‌یاران | قضات دادگاه‌های اداری، دادرسان و مأموران استماع | قضات دادگاه و دادیاران | تندنویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | کارشناسان انطباق و نظارت قانونی | کارشناسان امور نظارتی و تنظیم مقررات | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان منابع انسانی | دبیران و مسئولان دفاتر حقوقی | مسئولان دفاتر و مدیران اجرایی | کارشناسان مدیریت اسناد | تحلیل‌گران و مشاوران مدیریت | استادان حقوق، آموزش عالی | بازرسان، کارشناسان و تحلیل‌گران بررسی تقلب و تخلفات | کارشناسان صدور و ارزیابی ریسک بیمه | کارشناسان ارزیابی و بازرسی مالی</t>
+          <t>کارشناسان و دستیاران امور حقوقی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | کارشناسان پژوهش و تحریر قضایی | وکلا | داوران، میانجی‌گران و صلح‌یاران | قضات دادگاه‌های اداری، دادرسان و مأموران استماع | قضات دادگاه و دادیاران | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان منابع انسانی | منشی‌ها و دستیاران اداری دفاتر حقوقی | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارشناسان مدیریت اسناد و مدارک | کارشناسان تحلیل مدیریت و روش‌ها | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان بازرسی، کشف و تحلیل تقلب | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | بازرسان و ارزیابان مالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | مدیریت و امور اداری | اقتصاد و حسابداری | ریاضیات | حقوق و مقررات دولتی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | امور کارکنان و منابع انسانی | ارتباطات و رسانه | روان‌شناسی | امور اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | قانون و دولت | رایانه و الکترونیک | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | محاسبات عددی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | توجه انتخابی</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | اصالت | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | تحلیل‌گران هوش تجاری | معلمان آموزش‌های فنی و حرفه‌ای، دوره متوسطه اول | مربیان و مدرسان فنی و حرفه‌ای، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای، دوره متوسطه دوم | استادان علوم ارتباطات، آموزش عالی | استادان علوم رایانه، آموزش عالی | استادان اقتصاد، آموزش عالی | مدیران امور آموزشی، آموزش عالی | استادان علوم تربیتی و آموزش، آموزش عالی | استادان علوم خانواده و مصرف‌کننده، آموزش عالی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | استادان حقوق، آموزش عالی | استادان علوم کتابداری، آموزش عالی | تحلیل‌گران و مشاوران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | استادان علوم سیاسی، آموزش عالی | استادان مددکاری اجتماعی، آموزش عالی | دستیاران آموزشی و حل تمرین، آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | تحلیل‌گران هوش تجاری | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | استادان اقتصاد دانشگاه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | استادان علوم سیاسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | دستیاران آموزشی در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | مهندسی و فناوری | مدیریت و امور اداری | طراحی | امور اداری | ایمنی و امنیت عمومی | ارتباطات و رسانه | امور کارکنان و منابع انسانی | مخابرات و ارتباطات از راه دور | اقتصاد و حسابداری | حقوق و مقررات دولتی</t>
+          <t>رایانه و الکترونیک | آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | مهندسی و فناوری | مدیریت و اداره | طراحی | اداری | ایمنی و امنیت عمومی | ارتباطات و رسانه | پرسنل و منابع انسانی | مخابرات | اقتصاد و حسابداری | قانون و دولت</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | محاسبات عددی | استدلال ریاضی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای، دوره متوسطه اول | مربیان و مدرسان فنی و حرفه‌ای، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای، دوره متوسطه دوم | استادان علوم ارتباطات، آموزش عالی | مهندسان سخت‌افزار رایانه | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | دانشمندان و پژوهشگران علوم رایانه و اطلاعات | مدیران سیستم‌های رایانه‌ای و فناوری اطلاعات | استادان علوم مهندسی، آموزش عالی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | استادان علوم کتابداری، آموزش عالی | تحلیل‌گران و مشاوران مدیریت | استادان علوم ریاضی، آموزش عالی | استادان فیزیک، آموزش عالی | توسعه‌دهندگان نرم‌افزار | دستیاران آموزشی و حل تمرین، آموزش عالی | مدرسان خصوصی و معلمان کمکی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | پژوهشگران علوم رایانه و اطلاعات | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان تحلیل مدیریت و روش‌ها | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | توسعه‌دهندگان نرم‌افزار | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
